--- a/MyBooking/data/login_data.xlsx
+++ b/MyBooking/data/login_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ukeya\Documents\Automation framework\MyBooking\MyBooking\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FCBEDB-3475-4611-906C-F0DBE73AD267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A8EB4E-FDB8-4961-AA76-905B9E70FE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>username</t>
   </si>
@@ -50,80 +50,80 @@
     <t>expected_result</t>
   </si>
   <si>
-    <t>Kollinumber</t>
-  </si>
-  <si>
-    <t>ExcelSenderName</t>
-  </si>
-  <si>
-    <t>ExcelReceiverName</t>
-  </si>
-  <si>
-    <t>ExcelconsignmentNo</t>
-  </si>
-  <si>
-    <t>ExcelSenderAddress1</t>
-  </si>
-  <si>
-    <t>ExcelReceiverAddress1</t>
-  </si>
-  <si>
-    <t>ExcelSenderPostalCode</t>
-  </si>
-  <si>
-    <t>ExcelReceiverPostalCode</t>
-  </si>
-  <si>
-    <t>ExcelEvent</t>
-  </si>
-  <si>
     <t>success</t>
   </si>
   <si>
-    <t>KS000170305NO</t>
-  </si>
-  <si>
-    <t>AMAZON.COM</t>
-  </si>
-  <si>
-    <t>STEINAR FJELDVANG</t>
-  </si>
-  <si>
-    <t>70438109631231509</t>
-  </si>
-  <si>
-    <t>AMAZON ROAD 100</t>
-  </si>
-  <si>
-    <t>FJELLVEIEN 24</t>
-  </si>
-  <si>
-    <t>US 00000 USA</t>
-  </si>
-  <si>
-    <t>NO 1467 STRØMMEN</t>
-  </si>
-  <si>
-    <t>FE</t>
-  </si>
-  <si>
     <t>SETCSARYUK</t>
   </si>
   <si>
     <t>mybooking</t>
+  </si>
+  <si>
+    <t>minPallets</t>
+  </si>
+  <si>
+    <t>customerNumber</t>
+  </si>
+  <si>
+    <t>postalCode</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>ediType</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Incoming Check</t>
+  </si>
+  <si>
+    <t>Testing Arya</t>
+  </si>
+  <si>
+    <t>Consolidate Duplicates</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Testing Edit Arya</t>
+  </si>
+  <si>
+    <t>Denmark</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF4F4F4F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF4F4F4F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -146,9 +146,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -491,11 +496,13 @@
     <col min="3" max="3" width="22.26953125" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="16.54296875" customWidth="1"/>
-    <col min="7" max="7" width="22.1796875" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" customWidth="1"/>
+    <col min="8" max="8" width="14.1796875" customWidth="1"/>
+    <col min="9" max="9" width="14.90625" customWidth="1"/>
     <col min="10" max="10" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,70 +512,72 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>20006439564</v>
+      </c>
+      <c r="F2" s="4">
+        <v>74601</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>20000194207</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2650</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="I3" t="s">
         <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/MyBooking/data/login_data.xlsx
+++ b/MyBooking/data/login_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ukeya\Documents\Automation framework\MyBooking\MyBooking\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ukeya\Automation\MyBooking\MyBooking\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A8EB4E-FDB8-4961-AA76-905B9E70FE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C89195-4FD2-4ABE-AC90-69B65F7C7BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16210" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>username</t>
   </si>
@@ -93,6 +93,30 @@
   </si>
   <si>
     <t>Denmark</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>arya.ukey@posten.no</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Test AR</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>Test AR message</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>AR MyBooking</t>
   </si>
 </sst>
 </file>
@@ -488,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -502,7 +526,7 @@
     <col min="10" max="10" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -530,8 +554,20 @@
       <c r="I1" t="s">
         <v>11</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -559,8 +595,20 @@
       <c r="I2" t="s">
         <v>13</v>
       </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D3">
         <v>2</v>
       </c>

--- a/MyBooking/data/login_data.xlsx
+++ b/MyBooking/data/login_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ukeya\Automation\MyBooking\MyBooking\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\Mybooking\MyBooking\MyBooking\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C89195-4FD2-4ABE-AC90-69B65F7C7BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789F3868-E5CC-4BF6-8535-210894C67851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16210" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,12 +53,6 @@
     <t>success</t>
   </si>
   <si>
-    <t>SETCSARYUK</t>
-  </si>
-  <si>
-    <t>mybooking</t>
-  </si>
-  <si>
     <t>minPallets</t>
   </si>
   <si>
@@ -80,27 +74,18 @@
     <t>Incoming Check</t>
   </si>
   <si>
-    <t>Testing Arya</t>
-  </si>
-  <si>
     <t>Consolidate Duplicates</t>
   </si>
   <si>
     <t>Sweden</t>
   </si>
   <si>
-    <t>Testing Edit Arya</t>
-  </si>
-  <si>
     <t>Denmark</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>arya.ukey@posten.no</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -117,6 +102,21 @@
   </si>
   <si>
     <t>AR MyBooking</t>
+  </si>
+  <si>
+    <t>Testing Automation</t>
+  </si>
+  <si>
+    <t>Testing AutomationEditOption</t>
+  </si>
+  <si>
+    <t>SETCSSENN1</t>
+  </si>
+  <si>
+    <t>sweden</t>
+  </si>
+  <si>
+    <t>senna.kamatchi.prabhakar@posten.no</t>
   </si>
 </sst>
 </file>
@@ -537,42 +537,42 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" t="s">
-        <v>11</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -587,25 +587,25 @@
         <v>74601</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -619,13 +619,13 @@
         <v>2650</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/MyBooking/data/login_data.xlsx
+++ b/MyBooking/data/login_data.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ukeya\Automation\MyBooking\MyBooking\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C89195-4FD2-4ABE-AC90-69B65F7C7BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DB1D81-E3D3-47AE-83BB-6F7B9F52033F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16210" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16210" windowHeight="8170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="RegisterOrder" sheetId="3" r:id="rId2"/>
+    <sheet name="CustomerNumber" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>username</t>
   </si>
@@ -117,6 +119,51 @@
   </si>
   <si>
     <t>AR MyBooking</t>
+  </si>
+  <si>
+    <t>CustomerNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CustomerNumber </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Address         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PostalCode </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Weight </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Parcels </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pallets </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OrderType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10000005156    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> test address AR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 74601      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> STK</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FDX</t>
   </si>
 </sst>
 </file>
@@ -633,6 +680,111 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7D75466-9119-4237-8855-973B63F41C1A}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>20024613505</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>55315</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260AB6B8-F02B-4914-A1C4-063449795F5A}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>10000005156</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{644fb37b-915b-49e6-8af0-243b8ee4c503}" enabled="1" method="Standard" siteId="{a1ae5425-0bde-496e-8c5a-8a06b0d94277}" removed="0"/>
